--- a/data_input/sugc_terrain_constraints_irr.xlsx
+++ b/data_input/sugc_terrain_constraints_irr.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pyaez_github_test_env\input\maize_sugarcane_reduction_tables\M5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dario_outputs\maize_sugarcane_reduction_tables\M5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4F0CC3-6429-4B9C-9BDF-D51B0D900AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA603C8-27F1-46AC-868A-7AD49202E829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{EE6CACD0-8D83-4948-BDC7-999A08C64FDC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{EE6CACD0-8D83-4948-BDC7-999A08C64FDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,22 +65,22 @@
     <t>0,1300</t>
   </si>
   <si>
+    <t>1300,1800</t>
+  </si>
+  <si>
+    <t>1800,2200</t>
+  </si>
+  <si>
+    <t>2200,2500</t>
+  </si>
+  <si>
+    <t>2500,2700</t>
+  </si>
+  <si>
+    <t>2700,10000</t>
+  </si>
+  <si>
     <t>45,100</t>
-  </si>
-  <si>
-    <t>1300,1800</t>
-  </si>
-  <si>
-    <t>1800,2200</t>
-  </si>
-  <si>
-    <t>2200,2500</t>
-  </si>
-  <si>
-    <t>2500,2700</t>
-  </si>
-  <si>
-    <t>2700,10000</t>
   </si>
 </sst>
 </file>
@@ -437,6 +437,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -464,8 +465,8 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>9</v>
+      <c r="I1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -499,7 +500,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -528,7 +529,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -557,7 +558,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -586,7 +587,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -615,7 +616,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>100</v>
